--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.56365949761616</v>
+        <v>3.666594668362626</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6519604652656</v>
+        <v>3.030943575605661</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9055833218183</v>
+        <v>1.772157289795474</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1629347367304</v>
+        <v>2.13897689471869</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.11883455563582</v>
+        <v>3.106810615290821</v>
       </c>
       <c r="D3" t="n">
-        <v>14.67342447096981</v>
+        <v>2.384431476532594</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9055833218183</v>
+        <v>1.772157289795474</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1629347367304</v>
+        <v>2.13897689471869</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.17346440481775</v>
+        <v>3.928187965782885</v>
       </c>
       <c r="D4" t="n">
-        <v>4.934114236757273</v>
+        <v>0.8017935634730569</v>
       </c>
       <c r="E4" t="n">
-        <v>10.9055833218183</v>
+        <v>1.772157289795474</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1629347367304</v>
+        <v>2.13897689471869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.49062514431602</v>
+        <v>8.042226585951354</v>
       </c>
       <c r="D5" t="n">
-        <v>44.41063329608274</v>
+        <v>7.216727910613445</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9055833218183</v>
+        <v>1.772157289795474</v>
       </c>
       <c r="F5" t="n">
-        <v>13.1629347367304</v>
+        <v>2.13897689471869</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.79587592908918</v>
+        <v>5.329329838476991</v>
       </c>
       <c r="D6" t="n">
-        <v>25.00445412576503</v>
+        <v>4.063223795436818</v>
       </c>
       <c r="E6" t="n">
-        <v>10.9055833218183</v>
+        <v>1.772157289795474</v>
       </c>
       <c r="F6" t="n">
-        <v>13.1629347367304</v>
+        <v>2.13897689471869</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
